--- a/artfynd/A 51547-2023 artfynd.xlsx
+++ b/artfynd/A 51547-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113203600</v>
+        <v>113203880</v>
       </c>
       <c r="B2" t="n">
-        <v>91290</v>
+        <v>97314</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,28 +687,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -716,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337042</v>
+        <v>337093</v>
       </c>
       <c r="R2" t="n">
-        <v>6560485</v>
+        <v>6560532</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113203332</v>
+        <v>113203296</v>
       </c>
       <c r="B3" t="n">
-        <v>96261</v>
+        <v>95590</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337273</v>
+        <v>337267</v>
       </c>
       <c r="R3" t="n">
-        <v>6560459</v>
+        <v>6560480</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113203296</v>
+        <v>113202647</v>
       </c>
       <c r="B4" t="n">
-        <v>95574</v>
+        <v>97314</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,28 +917,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2569</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -942,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337267</v>
+        <v>337253</v>
       </c>
       <c r="R4" t="n">
-        <v>6560480</v>
+        <v>6560489</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +985,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +995,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113202850</v>
+        <v>113203600</v>
       </c>
       <c r="B5" t="n">
-        <v>97298</v>
+        <v>91306</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,43 +1034,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kotjärnet (Kotjärnet), Dls</t>
+          <t>Tjäregraven (Tjäregraven), Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337237</v>
+        <v>337042</v>
       </c>
       <c r="R5" t="n">
-        <v>6560502</v>
+        <v>6560485</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1104,7 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113203880</v>
+        <v>113203332</v>
       </c>
       <c r="B6" t="n">
-        <v>97298</v>
+        <v>96277</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,43 +1147,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tjäregraven (Tjäregraven), Dls</t>
+          <t>Kotjärnet (Kotjärnet), Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337093</v>
+        <v>337273</v>
       </c>
       <c r="R6" t="n">
-        <v>6560532</v>
+        <v>6560459</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,7 +1251,7 @@
         <v>113203083</v>
       </c>
       <c r="B7" t="n">
-        <v>104364</v>
+        <v>104380</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1361,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113202647</v>
+        <v>113202850</v>
       </c>
       <c r="B8" t="n">
-        <v>97298</v>
+        <v>97314</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1406,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>337253</v>
+        <v>337237</v>
       </c>
       <c r="R8" t="n">
-        <v>6560489</v>
+        <v>6560502</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,7 +1481,7 @@
         <v>113203743</v>
       </c>
       <c r="B9" t="n">
-        <v>91290</v>
+        <v>91306</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 51547-2023 artfynd.xlsx
+++ b/artfynd/A 51547-2023 artfynd.xlsx
@@ -1361,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113202850</v>
+        <v>113203743</v>
       </c>
       <c r="B8" t="n">
-        <v>97314</v>
+        <v>91306</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,43 +1373,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kotjärnet (Kotjärnet), Dls</t>
+          <t>Tjäregraven (Tjäregraven), Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>337237</v>
+        <v>336923</v>
       </c>
       <c r="R8" t="n">
-        <v>6560502</v>
+        <v>6560496</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113203743</v>
+        <v>113202850</v>
       </c>
       <c r="B9" t="n">
-        <v>91306</v>
+        <v>97314</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,39 +1486,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tjäregraven (Tjäregraven), Dls</t>
+          <t>Kotjärnet (Kotjärnet), Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>336923</v>
+        <v>337237</v>
       </c>
       <c r="R9" t="n">
-        <v>6560496</v>
+        <v>6560502</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 51547-2023 artfynd.xlsx
+++ b/artfynd/A 51547-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113203880</v>
+        <v>113202647</v>
       </c>
       <c r="B2" t="n">
         <v>97314</v>
@@ -710,20 +710,20 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tjäregraven (Tjäregraven), Dls</t>
+          <t>Kotjärnet (Kotjärnet), Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337093</v>
+        <v>337253</v>
       </c>
       <c r="R2" t="n">
-        <v>6560532</v>
+        <v>6560489</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113203296</v>
+        <v>113203332</v>
       </c>
       <c r="B3" t="n">
-        <v>95590</v>
+        <v>96277</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2569</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337267</v>
+        <v>337273</v>
       </c>
       <c r="R3" t="n">
-        <v>6560480</v>
+        <v>6560459</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113202647</v>
+        <v>113203296</v>
       </c>
       <c r="B4" t="n">
-        <v>97314</v>
+        <v>95590</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,32 +917,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -950,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337253</v>
+        <v>337267</v>
       </c>
       <c r="R4" t="n">
-        <v>6560489</v>
+        <v>6560480</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -995,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113203600</v>
+        <v>113202850</v>
       </c>
       <c r="B5" t="n">
-        <v>91306</v>
+        <v>97314</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,39 +1030,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tjäregraven (Tjäregraven), Dls</t>
+          <t>Kotjärnet (Kotjärnet), Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337042</v>
+        <v>337237</v>
       </c>
       <c r="R5" t="n">
-        <v>6560485</v>
+        <v>6560502</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113203332</v>
+        <v>113203743</v>
       </c>
       <c r="B6" t="n">
-        <v>96277</v>
+        <v>91306</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,35 +1151,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kotjärnet (Kotjärnet), Dls</t>
+          <t>Tjäregraven (Tjäregraven), Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337273</v>
+        <v>336923</v>
       </c>
       <c r="R6" t="n">
-        <v>6560459</v>
+        <v>6560496</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113203083</v>
+        <v>113203880</v>
       </c>
       <c r="B7" t="n">
-        <v>104380</v>
+        <v>97314</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,39 +1260,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kotjärnet (Kotjärnet), Dls</t>
+          <t>Tjäregraven (Tjäregraven), Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>337233</v>
+        <v>337093</v>
       </c>
       <c r="R7" t="n">
-        <v>6560466</v>
+        <v>6560532</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,7 +1365,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113203743</v>
+        <v>113203600</v>
       </c>
       <c r="B8" t="n">
         <v>91306</v>
@@ -1402,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>336923</v>
+        <v>337042</v>
       </c>
       <c r="R8" t="n">
-        <v>6560496</v>
+        <v>6560485</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113202850</v>
+        <v>113203083</v>
       </c>
       <c r="B9" t="n">
-        <v>97314</v>
+        <v>104380</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,32 +1490,28 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>337237</v>
+        <v>337233</v>
       </c>
       <c r="R9" t="n">
-        <v>6560502</v>
+        <v>6560466</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 51547-2023 artfynd.xlsx
+++ b/artfynd/A 51547-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113202647</v>
+        <v>113203743</v>
       </c>
       <c r="B2" t="n">
-        <v>97314</v>
+        <v>91318</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kotjärnet (Kotjärnet), Dls</t>
+          <t>Tjäregraven (Tjäregraven), Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337253</v>
+        <v>336923</v>
       </c>
       <c r="R2" t="n">
-        <v>6560489</v>
+        <v>6560496</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +751,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +761,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113203332</v>
+        <v>113203600</v>
       </c>
       <c r="B3" t="n">
-        <v>96277</v>
+        <v>91318</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,35 +804,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kotjärnet (Kotjärnet), Dls</t>
+          <t>Tjäregraven (Tjäregraven), Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337273</v>
+        <v>337042</v>
       </c>
       <c r="R3" t="n">
-        <v>6560459</v>
+        <v>6560485</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113203296</v>
+        <v>113203332</v>
       </c>
       <c r="B4" t="n">
-        <v>95590</v>
+        <v>96289</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,21 +917,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2569</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -946,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337267</v>
+        <v>337273</v>
       </c>
       <c r="R4" t="n">
-        <v>6560480</v>
+        <v>6560459</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113202850</v>
+        <v>113203296</v>
       </c>
       <c r="B5" t="n">
-        <v>97314</v>
+        <v>95602</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,32 +1026,28 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2569</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1063,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337237</v>
+        <v>337267</v>
       </c>
       <c r="R5" t="n">
-        <v>6560502</v>
+        <v>6560480</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113203743</v>
+        <v>113202647</v>
       </c>
       <c r="B6" t="n">
-        <v>91306</v>
+        <v>97326</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,39 +1139,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tjäregraven (Tjäregraven), Dls</t>
+          <t>Kotjärnet (Kotjärnet), Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>336923</v>
+        <v>337253</v>
       </c>
       <c r="R6" t="n">
-        <v>6560496</v>
+        <v>6560489</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113203880</v>
+        <v>113203083</v>
       </c>
       <c r="B7" t="n">
-        <v>97314</v>
+        <v>104394</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,43 +1256,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tjäregraven (Tjäregraven), Dls</t>
+          <t>Kotjärnet (Kotjärnet), Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>337093</v>
+        <v>337233</v>
       </c>
       <c r="R7" t="n">
-        <v>6560532</v>
+        <v>6560466</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113203600</v>
+        <v>113203880</v>
       </c>
       <c r="B8" t="n">
-        <v>91306</v>
+        <v>97326</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,28 +1369,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1406,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>337042</v>
+        <v>337093</v>
       </c>
       <c r="R8" t="n">
-        <v>6560485</v>
+        <v>6560532</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113203083</v>
+        <v>113202850</v>
       </c>
       <c r="B9" t="n">
-        <v>104380</v>
+        <v>97326</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,28 +1486,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>337233</v>
+        <v>337237</v>
       </c>
       <c r="R9" t="n">
-        <v>6560466</v>
+        <v>6560502</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 51547-2023 artfynd.xlsx
+++ b/artfynd/A 51547-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113203743</v>
+        <v>113202850</v>
       </c>
       <c r="B2" t="n">
-        <v>91318</v>
+        <v>97326</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tjäregraven (Tjäregraven), Dls</t>
+          <t>Kotjärnet (Kotjärnet), Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>336923</v>
+        <v>337237</v>
       </c>
       <c r="R2" t="n">
-        <v>6560496</v>
+        <v>6560502</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -901,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113203332</v>
+        <v>113203296</v>
       </c>
       <c r="B4" t="n">
-        <v>96289</v>
+        <v>95602</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,21 +921,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337273</v>
+        <v>337267</v>
       </c>
       <c r="R4" t="n">
-        <v>6560459</v>
+        <v>6560480</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113203296</v>
+        <v>113203083</v>
       </c>
       <c r="B5" t="n">
-        <v>95602</v>
+        <v>104394</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,21 +1034,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2569</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337267</v>
+        <v>337233</v>
       </c>
       <c r="R5" t="n">
-        <v>6560480</v>
+        <v>6560466</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1094,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1104,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,7 +1131,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113202647</v>
+        <v>113203880</v>
       </c>
       <c r="B6" t="n">
         <v>97326</v>
@@ -1162,20 +1166,20 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kotjärnet (Kotjärnet), Dls</t>
+          <t>Tjäregraven (Tjäregraven), Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337253</v>
+        <v>337093</v>
       </c>
       <c r="R6" t="n">
-        <v>6560489</v>
+        <v>6560532</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113203083</v>
+        <v>113203332</v>
       </c>
       <c r="B7" t="n">
-        <v>104394</v>
+        <v>96289</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,21 +1264,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>337233</v>
+        <v>337273</v>
       </c>
       <c r="R7" t="n">
-        <v>6560466</v>
+        <v>6560459</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,7 +1361,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113203880</v>
+        <v>113202647</v>
       </c>
       <c r="B8" t="n">
         <v>97326</v>
@@ -1392,20 +1396,20 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tjäregraven (Tjäregraven), Dls</t>
+          <t>Kotjärnet (Kotjärnet), Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>337093</v>
+        <v>337253</v>
       </c>
       <c r="R8" t="n">
-        <v>6560532</v>
+        <v>6560489</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113202850</v>
+        <v>113203743</v>
       </c>
       <c r="B9" t="n">
-        <v>97326</v>
+        <v>91318</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,43 +1490,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kotjärnet (Kotjärnet), Dls</t>
+          <t>Tjäregraven (Tjäregraven), Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>337237</v>
+        <v>336923</v>
       </c>
       <c r="R9" t="n">
-        <v>6560502</v>
+        <v>6560496</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 51547-2023 artfynd.xlsx
+++ b/artfynd/A 51547-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113202850</v>
+        <v>113203332</v>
       </c>
       <c r="B2" t="n">
-        <v>97326</v>
+        <v>96311</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,32 +687,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -720,10 +716,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337237</v>
+        <v>337273</v>
       </c>
       <c r="R2" t="n">
-        <v>6560502</v>
+        <v>6560459</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +751,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +761,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113203600</v>
+        <v>113202850</v>
       </c>
       <c r="B3" t="n">
-        <v>91318</v>
+        <v>97348</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,39 +800,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjäregraven (Tjäregraven), Dls</t>
+          <t>Kotjärnet (Kotjärnet), Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337042</v>
+        <v>337237</v>
       </c>
       <c r="R3" t="n">
-        <v>6560485</v>
+        <v>6560502</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113203296</v>
+        <v>113203600</v>
       </c>
       <c r="B4" t="n">
-        <v>95602</v>
+        <v>91340</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,35 +921,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2569</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kotjärnet (Kotjärnet), Dls</t>
+          <t>Tjäregraven (Tjäregraven), Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337267</v>
+        <v>337042</v>
       </c>
       <c r="R4" t="n">
-        <v>6560480</v>
+        <v>6560485</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113203083</v>
+        <v>113202647</v>
       </c>
       <c r="B5" t="n">
-        <v>104394</v>
+        <v>97348</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,28 +1030,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337233</v>
+        <v>337253</v>
       </c>
       <c r="R5" t="n">
-        <v>6560466</v>
+        <v>6560489</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1104,7 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113203880</v>
+        <v>113203743</v>
       </c>
       <c r="B6" t="n">
-        <v>97326</v>
+        <v>91340</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,32 +1147,28 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337093</v>
+        <v>336923</v>
       </c>
       <c r="R6" t="n">
-        <v>6560532</v>
+        <v>6560496</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113203332</v>
+        <v>113203083</v>
       </c>
       <c r="B7" t="n">
-        <v>96289</v>
+        <v>104416</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,21 +1264,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1289,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>337273</v>
+        <v>337233</v>
       </c>
       <c r="R7" t="n">
-        <v>6560459</v>
+        <v>6560466</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113202647</v>
+        <v>113203296</v>
       </c>
       <c r="B8" t="n">
-        <v>97326</v>
+        <v>95624</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,32 +1373,28 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>2569</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1406,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>337253</v>
+        <v>337267</v>
       </c>
       <c r="R8" t="n">
-        <v>6560489</v>
+        <v>6560480</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113203743</v>
+        <v>113203880</v>
       </c>
       <c r="B9" t="n">
-        <v>91318</v>
+        <v>97348</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,28 +1486,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>336923</v>
+        <v>337093</v>
       </c>
       <c r="R9" t="n">
-        <v>6560496</v>
+        <v>6560532</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 51547-2023 artfynd.xlsx
+++ b/artfynd/A 51547-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113203332</v>
+        <v>113203600</v>
       </c>
       <c r="B2" t="n">
-        <v>96311</v>
+        <v>91344</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,35 +691,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kotjärnet (Kotjärnet), Dls</t>
+          <t>Tjäregraven (Tjäregraven), Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337273</v>
+        <v>337042</v>
       </c>
       <c r="R2" t="n">
-        <v>6560459</v>
+        <v>6560485</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,7 +751,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113202850</v>
+        <v>113202647</v>
       </c>
       <c r="B3" t="n">
-        <v>97348</v>
+        <v>97352</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337237</v>
+        <v>337253</v>
       </c>
       <c r="R3" t="n">
-        <v>6560502</v>
+        <v>6560489</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113203600</v>
+        <v>113203743</v>
       </c>
       <c r="B4" t="n">
-        <v>91340</v>
+        <v>91344</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337042</v>
+        <v>336923</v>
       </c>
       <c r="R4" t="n">
-        <v>6560485</v>
+        <v>6560496</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113202647</v>
+        <v>113202850</v>
       </c>
       <c r="B5" t="n">
-        <v>97348</v>
+        <v>97352</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337253</v>
+        <v>337237</v>
       </c>
       <c r="R5" t="n">
-        <v>6560489</v>
+        <v>6560502</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113203743</v>
+        <v>113203083</v>
       </c>
       <c r="B6" t="n">
-        <v>91340</v>
+        <v>104420</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,35 +1151,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tjäregraven (Tjäregraven), Dls</t>
+          <t>Kotjärnet (Kotjärnet), Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>336923</v>
+        <v>337233</v>
       </c>
       <c r="R6" t="n">
-        <v>6560496</v>
+        <v>6560466</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113203083</v>
+        <v>113203880</v>
       </c>
       <c r="B7" t="n">
-        <v>104416</v>
+        <v>97352</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,39 +1260,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kotjärnet (Kotjärnet), Dls</t>
+          <t>Tjäregraven (Tjäregraven), Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>337233</v>
+        <v>337093</v>
       </c>
       <c r="R7" t="n">
-        <v>6560466</v>
+        <v>6560532</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113203296</v>
+        <v>113203332</v>
       </c>
       <c r="B8" t="n">
-        <v>95624</v>
+        <v>96315</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,21 +1381,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2569</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>337267</v>
+        <v>337273</v>
       </c>
       <c r="R8" t="n">
-        <v>6560480</v>
+        <v>6560459</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113203880</v>
+        <v>113203296</v>
       </c>
       <c r="B9" t="n">
-        <v>97348</v>
+        <v>95628</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,43 +1490,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>2569</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tjäregraven (Tjäregraven), Dls</t>
+          <t>Kotjärnet (Kotjärnet), Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>337093</v>
+        <v>337267</v>
       </c>
       <c r="R9" t="n">
-        <v>6560532</v>
+        <v>6560480</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 51547-2023 artfynd.xlsx
+++ b/artfynd/A 51547-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113203600</v>
+        <v>113203083</v>
       </c>
       <c r="B2" t="n">
-        <v>91344</v>
+        <v>104420</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,35 +691,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tjäregraven (Tjäregraven), Dls</t>
+          <t>Kotjärnet (Kotjärnet), Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337042</v>
+        <v>337233</v>
       </c>
       <c r="R2" t="n">
-        <v>6560485</v>
+        <v>6560466</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,7 +751,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113202647</v>
+        <v>113203332</v>
       </c>
       <c r="B3" t="n">
-        <v>97352</v>
+        <v>96315</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -800,32 +800,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337253</v>
+        <v>337273</v>
       </c>
       <c r="R3" t="n">
-        <v>6560489</v>
+        <v>6560459</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113203743</v>
+        <v>113203296</v>
       </c>
       <c r="B4" t="n">
-        <v>91344</v>
+        <v>95628</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,35 +917,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjäregraven (Tjäregraven), Dls</t>
+          <t>Kotjärnet (Kotjärnet), Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>336923</v>
+        <v>337267</v>
       </c>
       <c r="R4" t="n">
-        <v>6560496</v>
+        <v>6560480</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,7 +1014,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113202850</v>
+        <v>113203880</v>
       </c>
       <c r="B5" t="n">
         <v>97352</v>
@@ -1053,20 +1049,20 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kotjärnet (Kotjärnet), Dls</t>
+          <t>Tjäregraven (Tjäregraven), Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337237</v>
+        <v>337093</v>
       </c>
       <c r="R5" t="n">
-        <v>6560502</v>
+        <v>6560532</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1094,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1104,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113203083</v>
+        <v>113202647</v>
       </c>
       <c r="B6" t="n">
-        <v>104420</v>
+        <v>97352</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,28 +1143,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337233</v>
+        <v>337253</v>
       </c>
       <c r="R6" t="n">
-        <v>6560466</v>
+        <v>6560489</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,7 +1248,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113203880</v>
+        <v>113202850</v>
       </c>
       <c r="B7" t="n">
         <v>97352</v>
@@ -1283,20 +1283,20 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tjäregraven (Tjäregraven), Dls</t>
+          <t>Kotjärnet (Kotjärnet), Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>337093</v>
+        <v>337237</v>
       </c>
       <c r="R7" t="n">
-        <v>6560532</v>
+        <v>6560502</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113203332</v>
+        <v>113203743</v>
       </c>
       <c r="B8" t="n">
-        <v>96315</v>
+        <v>91344</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,35 +1381,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kotjärnet (Kotjärnet), Dls</t>
+          <t>Tjäregraven (Tjäregraven), Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>337273</v>
+        <v>336923</v>
       </c>
       <c r="R8" t="n">
-        <v>6560459</v>
+        <v>6560496</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113203296</v>
+        <v>113203600</v>
       </c>
       <c r="B9" t="n">
-        <v>95628</v>
+        <v>91344</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,35 +1494,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2569</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kotjärnet (Kotjärnet), Dls</t>
+          <t>Tjäregraven (Tjäregraven), Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>337267</v>
+        <v>337042</v>
       </c>
       <c r="R9" t="n">
-        <v>6560480</v>
+        <v>6560485</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 51547-2023 artfynd.xlsx
+++ b/artfynd/A 51547-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113203083</v>
+        <v>113203332</v>
       </c>
       <c r="B2" t="n">
-        <v>104420</v>
+        <v>96321</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337233</v>
+        <v>337273</v>
       </c>
       <c r="R2" t="n">
-        <v>6560466</v>
+        <v>6560459</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,7 +751,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113203332</v>
+        <v>113203600</v>
       </c>
       <c r="B3" t="n">
-        <v>96315</v>
+        <v>91350</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,35 +804,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kotjärnet (Kotjärnet), Dls</t>
+          <t>Tjäregraven (Tjäregraven), Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337273</v>
+        <v>337042</v>
       </c>
       <c r="R3" t="n">
-        <v>6560459</v>
+        <v>6560485</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113203296</v>
+        <v>113202647</v>
       </c>
       <c r="B4" t="n">
-        <v>95628</v>
+        <v>97358</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,28 +913,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2569</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -942,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337267</v>
+        <v>337253</v>
       </c>
       <c r="R4" t="n">
-        <v>6560480</v>
+        <v>6560489</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,7 +1021,7 @@
         <v>113203880</v>
       </c>
       <c r="B5" t="n">
-        <v>97352</v>
+        <v>97358</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1131,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113202647</v>
+        <v>113203296</v>
       </c>
       <c r="B6" t="n">
-        <v>97352</v>
+        <v>95634</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,32 +1147,28 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337253</v>
+        <v>337267</v>
       </c>
       <c r="R6" t="n">
-        <v>6560489</v>
+        <v>6560480</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113202850</v>
+        <v>113203743</v>
       </c>
       <c r="B7" t="n">
-        <v>97352</v>
+        <v>91350</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,43 +1260,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kotjärnet (Kotjärnet), Dls</t>
+          <t>Tjäregraven (Tjäregraven), Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>337237</v>
+        <v>336923</v>
       </c>
       <c r="R7" t="n">
-        <v>6560502</v>
+        <v>6560496</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113203743</v>
+        <v>113203083</v>
       </c>
       <c r="B8" t="n">
-        <v>91344</v>
+        <v>104426</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,35 +1377,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tjäregraven (Tjäregraven), Dls</t>
+          <t>Kotjärnet (Kotjärnet), Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>336923</v>
+        <v>337233</v>
       </c>
       <c r="R8" t="n">
-        <v>6560496</v>
+        <v>6560466</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113203600</v>
+        <v>113202850</v>
       </c>
       <c r="B9" t="n">
-        <v>91344</v>
+        <v>97358</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,39 +1486,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tjäregraven (Tjäregraven), Dls</t>
+          <t>Kotjärnet (Kotjärnet), Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>337042</v>
+        <v>337237</v>
       </c>
       <c r="R9" t="n">
-        <v>6560485</v>
+        <v>6560502</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 51547-2023 artfynd.xlsx
+++ b/artfynd/A 51547-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113203332</v>
+        <v>113203600</v>
       </c>
       <c r="B2" t="n">
-        <v>96321</v>
+        <v>91350</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,35 +691,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kotjärnet (Kotjärnet), Dls</t>
+          <t>Tjäregraven (Tjäregraven), Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337273</v>
+        <v>337042</v>
       </c>
       <c r="R2" t="n">
-        <v>6560459</v>
+        <v>6560485</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,7 +751,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113203600</v>
+        <v>113203332</v>
       </c>
       <c r="B3" t="n">
-        <v>91350</v>
+        <v>96321</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,35 +804,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjäregraven (Tjäregraven), Dls</t>
+          <t>Kotjärnet (Kotjärnet), Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337042</v>
+        <v>337273</v>
       </c>
       <c r="R3" t="n">
-        <v>6560485</v>
+        <v>6560459</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,7 +901,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113202647</v>
+        <v>113202850</v>
       </c>
       <c r="B4" t="n">
         <v>97358</v>
@@ -936,7 +936,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337253</v>
+        <v>337237</v>
       </c>
       <c r="R4" t="n">
-        <v>6560489</v>
+        <v>6560502</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,7 +1018,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113203880</v>
+        <v>113202647</v>
       </c>
       <c r="B5" t="n">
         <v>97358</v>
@@ -1053,20 +1053,20 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tjäregraven (Tjäregraven), Dls</t>
+          <t>Kotjärnet (Kotjärnet), Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337093</v>
+        <v>337253</v>
       </c>
       <c r="R5" t="n">
-        <v>6560532</v>
+        <v>6560489</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113203296</v>
+        <v>113203743</v>
       </c>
       <c r="B6" t="n">
-        <v>95634</v>
+        <v>91350</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,35 +1151,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2569</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kotjärnet (Kotjärnet), Dls</t>
+          <t>Tjäregraven (Tjäregraven), Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337267</v>
+        <v>336923</v>
       </c>
       <c r="R6" t="n">
-        <v>6560480</v>
+        <v>6560496</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113203743</v>
+        <v>113203880</v>
       </c>
       <c r="B7" t="n">
-        <v>91350</v>
+        <v>97358</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,28 +1260,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1289,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>336923</v>
+        <v>337093</v>
       </c>
       <c r="R7" t="n">
-        <v>6560496</v>
+        <v>6560532</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113203083</v>
+        <v>113203296</v>
       </c>
       <c r="B8" t="n">
-        <v>104426</v>
+        <v>95634</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,21 +1381,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>2569</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>337233</v>
+        <v>337267</v>
       </c>
       <c r="R8" t="n">
-        <v>6560466</v>
+        <v>6560480</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113202850</v>
+        <v>113203083</v>
       </c>
       <c r="B9" t="n">
-        <v>97358</v>
+        <v>104426</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,32 +1490,28 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>337237</v>
+        <v>337233</v>
       </c>
       <c r="R9" t="n">
-        <v>6560502</v>
+        <v>6560466</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 51547-2023 artfynd.xlsx
+++ b/artfynd/A 51547-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51547-2023 artfynd.xlsx
+++ b/artfynd/A 51547-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>113203296</v>
       </c>
       <c r="B2" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -712,7 +707,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kotjärnet (Kotjärnet), Dls</t>
+          <t>Kotjärnet, Kotjärnet, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -788,51 +783,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113203083</v>
+        <v>113203600</v>
       </c>
       <c r="B3" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kotjärnet (Kotjärnet), Dls</t>
+          <t>Tjäregraven, Tjäregraven, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337233</v>
+        <v>337042</v>
       </c>
       <c r="R3" t="n">
-        <v>6560466</v>
+        <v>6560485</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,7 +854,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +864,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,51 +891,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113203332</v>
+        <v>113203743</v>
       </c>
       <c r="B4" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kotjärnet (Kotjärnet), Dls</t>
+          <t>Tjäregraven, Tjäregraven, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337273</v>
+        <v>336924</v>
       </c>
       <c r="R4" t="n">
-        <v>6560459</v>
+        <v>6560496</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +962,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +972,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,55 +999,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113203880</v>
+        <v>113203655</v>
       </c>
       <c r="B5" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tjäregraven (Tjäregraven), Dls</t>
+          <t>Tjäregraven, Tjäregraven, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337092</v>
+        <v>337011</v>
       </c>
       <c r="R5" t="n">
-        <v>6560532</v>
+        <v>6560488</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,7 +1070,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1104,7 +1080,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,15 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113202850</v>
+        <v>113202647</v>
       </c>
       <c r="B6" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1166,20 +1137,20 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kotjärnet (Kotjärnet), Dls</t>
+          <t>Kotjärnet, Kotjärnet, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337237</v>
+        <v>337253</v>
       </c>
       <c r="R6" t="n">
-        <v>6560501</v>
+        <v>6560489</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,7 +1182,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1192,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,51 +1219,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113203743</v>
+        <v>113202850</v>
       </c>
       <c r="B7" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tjäregraven (Tjäregraven), Dls</t>
+          <t>Kotjärnet, Kotjärnet, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>336924</v>
+        <v>337237</v>
       </c>
       <c r="R7" t="n">
-        <v>6560496</v>
+        <v>6560501</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,7 +1294,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1304,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,15 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113202647</v>
+        <v>113203880</v>
       </c>
       <c r="B8" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1396,20 +1361,20 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kotjärnet (Kotjärnet), Dls</t>
+          <t>Tjäregraven, Tjäregraven, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>337253</v>
+        <v>337092</v>
       </c>
       <c r="R8" t="n">
-        <v>6560489</v>
+        <v>6560532</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,7 +1406,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1416,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,15 +1443,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113203600</v>
+        <v>113203083</v>
       </c>
       <c r="B9" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,35 +1454,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tjäregraven (Tjäregraven), Dls</t>
+          <t>Kotjärnet, Kotjärnet, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>337042</v>
+        <v>337233</v>
       </c>
       <c r="R9" t="n">
-        <v>6560485</v>
+        <v>6560466</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1514,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1524,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1588,6 +1548,114 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>113203332</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kotjärnet, Kotjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>337273</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6560459</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vårvik</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51547-2023 artfynd.xlsx
+++ b/artfynd/A 51547-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113203296</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113203600</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113203743</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113203655</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1216,6 +1241,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113202647</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1328,6 +1358,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113202850</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1440,6 +1475,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113203880</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1548,6 +1588,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113203083</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1656,8 +1701,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113203332</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>